--- a/workout_backlog.xlsx
+++ b/workout_backlog.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -165,8 +165,24 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -218,6 +234,24 @@
         <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -245,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -346,10 +380,34 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -715,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -795,7 +853,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -835,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -875,7 +933,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -915,7 +973,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -955,7 +1013,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -995,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1035,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -1074,14 +1132,12 @@
       <c r="E9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1116,14 +1172,12 @@
       <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1158,14 +1212,12 @@
       <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1200,14 +1252,12 @@
       <c r="E12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1242,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1280,14 +1330,12 @@
       <c r="E14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1322,14 +1370,12 @@
       <c r="E15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1364,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1404,7 +1450,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
@@ -1444,7 +1490,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -1483,7 +1529,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -1561,7 +1607,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -1600,7 +1646,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -1639,7 +1685,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1678,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -1717,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1755,14 +1801,12 @@
       <c r="E26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -1796,14 +1840,12 @@
       <c r="E27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1837,14 +1879,12 @@
       <c r="E28" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1877,14 +1917,12 @@
       <c r="E29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -1918,7 +1956,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -1957,7 +1995,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
@@ -1996,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -2035,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
@@ -2074,7 +2112,7 @@
         <v>5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
@@ -2114,7 +2152,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
@@ -2153,7 +2191,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
@@ -2192,7 +2230,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2269,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -2269,14 +2307,12 @@
       <c r="E39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -2310,14 +2346,12 @@
       <c r="E40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F40" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -2351,14 +2385,12 @@
       <c r="E41" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -2392,7 +2424,7 @@
         <v>5</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -2432,7 +2464,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
@@ -2470,14 +2502,12 @@
       <c r="E44" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -2511,14 +2541,12 @@
       <c r="E45" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -2552,14 +2580,12 @@
       <c r="E46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -2594,7 +2620,7 @@
         <v>3</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
@@ -2633,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
@@ -2672,7 +2698,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
@@ -2710,14 +2736,12 @@
       <c r="E50" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F50" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -2751,14 +2775,12 @@
       <c r="E51" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F51" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -2791,14 +2813,12 @@
       <c r="E52" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F52" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -2832,14 +2852,12 @@
       <c r="E53" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -2874,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
@@ -2913,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
@@ -2952,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -2991,7 +3009,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -3006,80 +3024,84 @@
       </c>
     </row>
     <row r="58" ht="52" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t>Профиль</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="35" t="inlineStr">
         <is>
           <t>Как пользователь я хочу зарегистрироваться чтобы создать аккаунт</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="34" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E58" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="n">
+      <c r="E58" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>Форма: email + пароль
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="H58" s="36" t="inlineStr">
+        <is>
+          <t>✅ Completed Sprint 1. Implemented via Firebase Auth email/password + Firestore user profile creation.
+--- Original AC ---
+Форма: email + пароль
 Firebase Auth регистрация
 Переход на главный экран после</t>
         </is>
       </c>
     </row>
     <row r="59" ht="52" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>Профиль</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="35" t="inlineStr">
         <is>
           <t>Как пользователь я хочу войти в аккаунт чтобы получить доступ к своим данным</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="34" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="n">
+      <c r="E59" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Форма: email + пароль
+      <c r="G59" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="H59" s="36" t="inlineStr">
+        <is>
+          <t>✅ Completed Sprint 1. LoginScreen with validation, error SnackBars, authStateProvider stream.
+--- Original AC ---
+Форма: email + пароль
 Firebase Auth логин
 Ошибки валидации</t>
         </is>
@@ -3110,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -3126,40 +3148,42 @@
       </c>
     </row>
     <row r="61" ht="52" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>Профиль</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="35" t="inlineStr">
         <is>
           <t>Как пользователь я хочу сбросить пароль чтобы восстановить доступ</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Ссылка "Забыл пароль" на экране логина
+      <c r="E61" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>✅ Completed Sprint 1. "Forgot password?" link sends Firebase reset email.
+--- Original AC ---
+Ссылка "Забыл пароль" на экране логина
 Firebase отправляет email
 Подтверждение отправки</t>
         </is>
@@ -3190,7 +3214,7 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -3206,40 +3230,42 @@
       </c>
     </row>
     <row r="63" ht="52" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>Профиль</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="38" t="inlineStr">
         <is>
           <t>Как пользователь я хочу войти через Google</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="37" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="n">
+      <c r="E63" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Кнопка Google Sign-In на экране логина
+      <c r="G63" s="37" t="inlineStr">
+        <is>
+          <t>[✕] Вырезано</t>
+        </is>
+      </c>
+      <c r="H63" s="39" t="inlineStr">
+        <is>
+          <t>❌ Cut to post-MVP per ADR-65. Setup overhead (SHA-1 keystore, google_sign_in 7.x API) did not justify value for student defense. Kept as disabled UI placeholder.
+--- Original AC ---
+Кнопка Google Sign-In на экране логина
 Firebase Google Auth
 Автоматическое создание профиля</t>
         </is>
@@ -3270,7 +3296,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
@@ -3309,14 +3335,12 @@
       <c r="E65" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F65" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -3351,14 +3375,12 @@
       <c r="E66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F66" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -3393,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
@@ -3472,7 +3494,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
@@ -3488,40 +3510,42 @@
       </c>
     </row>
     <row r="70" ht="52" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
+      <c r="A70" s="34" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="35" t="inlineStr">
         <is>
           <t>Как пользователь я хочу видеть splash screen при запуске</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="E70" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Логотип на тёмном фоне
+      <c r="G70" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>✅ Completed Sprint 1. Splash screen with logo, tagline, lazy progress bar (800ms fade-in per ADR-36).
+--- Original AC ---
+Логотип на тёмном фоне
 Плавный переход на главный экран</t>
         </is>
       </c>
@@ -3605,40 +3629,42 @@
       </c>
     </row>
     <row r="73" ht="52" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="A73" s="34" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="35" t="inlineStr">
         <is>
           <t>Как пользователь я хочу использовать bottom navigation bar</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="34" t="inlineStr">
         <is>
           <t>Must Have</t>
         </is>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="n">
+      <c r="E73" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>5 вкладок: Home, History, FAB, Exercises, Profile
+      <c r="G73" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>✅ Completed Sprint 1. MainShell with ShellRoute, 5-tab bottom nav, center Start FAB button.
+--- Original AC ---
+5 вкладок: Home, History, FAB, Exercises, Profile
 Активная вкладка подсвечивается</t>
         </is>
       </c>
@@ -3668,7 +3694,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
@@ -3707,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
@@ -3746,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
@@ -3785,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
@@ -3824,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
@@ -3863,14 +3889,12 @@
       <c r="E79" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F79" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -3904,14 +3928,12 @@
       <c r="E80" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -3946,14 +3968,12 @@
       <c r="E81" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F81" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -3988,7 +4008,7 @@
         <v>2</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
@@ -4027,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
@@ -4065,14 +4085,12 @@
       <c r="E84" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F84" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -4106,14 +4124,12 @@
       <c r="E85" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F85" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -4147,14 +4163,12 @@
       <c r="E86" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F86" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -4188,14 +4202,12 @@
       <c r="E87" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F87" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -4229,380 +4241,18 @@
       <c r="E88" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
+      <c r="F88" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
+          <t>[ ] Не начато</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
           <t>Свайп вниз обновляет данные на экране
 Индикатор загрузки при обновлении</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу продолжить незавершённую тренировку чтобы не потерять прогресс</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>На главном экране banner если есть workout с finishedAt==null\nТап на Resume — открывает Active Workout с восстановленным состоянием\nТап Discard — удаляет незавершённую тренировку</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу создать новое упражнение из пустого поиска чтобы быстро добавить нестандартное</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Should Have</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Если поиск не нашёл результатов — кнопка 'Create {query}'\nПереход в форму создания с pre-filled именем\nПосле создания — возврат в библиотеку</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу использовать custom numpad для ввода веса и повторений чтобы быстро логировать</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>Bottom sheet с крупными цифровыми кнопками (мин 56×56px)\nТолько цифры + dot + backspace + Done\nHeader показывает что редактируется</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу чтобы новый подход заполнялся значениями прошлой тренировки чтобы не вводить повторно</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>При Add set — weight/reps pre-filled из того же номера подхода прошлой тренировки\nЕсли такого номера нет — из последнего подхода текущей тренировки\nЕсли первая тренировка — пустые поля</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу чтобы PR считался по estimated 1RM формуле для справедливого сравнения</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Формула Epley: weight × (1 + reps/30)\nPR хранится как best set\nБейдж 🏆 на подходе при новом PR\nCongrats bottom sheet при завершении тренировки</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу видеть гистограмму частоты тренировок чтобы оценить регулярность</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Should Have</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>BarChart: тренировок по периодам\nЕдиницы X зависят от period (день/неделя/месяц)\nНа экране Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу выбирать упражнения через bottom sheet с multi-select чтобы быстро добавить несколько</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Bottom sheet 85% высоты\nПоиск + фильтр по мышцам (переиспользует Library)\nЧекбоксы, кнопка 'Add (N) selected'\nДубликаты disabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу менять порядок упражнений перетаскиванием чтобы организовать тренировку</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Should Have</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Drag handle на каждом упражнении\nReorderableListView\nПорядок сохраняется в Firestore\nРаботает в Workout Start и Active Workout</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу чтобы удаление кастомного упражнения не ломало старые тренировки</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Soft delete: isDeleted=true flag\nНе показывается в Library\nВ старых workouts название отображается корректно\nPR по этому exercise сохраняется</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Как пользователь я хочу видеть индикатор отсутствия интернета чтобы понимать работаю offline</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Should Have</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr">
-        <is>
-          <t>Badge (иконка wifi-off) в AppBar при offline\nБаннер 'You're offline. Using cached data.'\nАвтоматически скрывается при восстановлении сети</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4663,17 +4313,17 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Зарегистрироваться</t>
+          <t>Создать тренировку</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>Профиль</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -4681,103 +4331,115 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F2" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Войти в аккаунт</t>
+          <t>Видеть активную тренировку</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Профиль</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Войти через google</t>
+          <t>Завершить тренировку</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Профиль</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Видеть splash screen при запуске</t>
+          <t>Видеть историю тренировок</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Приложение</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F5" s="16" t="n"/>
+      <c r="F5" s="16" t="inlineStr"/>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Использовать bottom navigation bar</t>
+          <t>Открыть детали тренировки</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Приложение</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -4788,267 +4450,275 @@
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F6" s="16" t="n"/>
+      <c r="F6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Получать toast уведомления об успешных действиях</t>
+          <t>Видеть длительность тренировки</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Приложение</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Назвать тренировку</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Видеть empty state на пустых экранах</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="n"/>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Видеть индикатор отсутствия интернета</t>
+          <t>Выбрать готовый шаблон тренировки</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Приложение</t>
+          <t>Тренировки</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Сохранить тренировку как шаблон</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Редактировать шаблон</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Удалить шаблон</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Создать тренировку</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Удалить тренировку</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Тренировки</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Дублировать прошлую тренировку</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Добавить заметку к тренировке</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Тренировки</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Назвать тренировку</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Отменить активную тренировку</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Тренировки</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Видеть библиотеку упражнений</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Искать упражнение по названию</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Фильтровать по группе мышц</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Создать своё упражнение</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Создать новое упражнение из пустого поиска</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F16" s="16" t="n"/>
+      <c r="F16" s="16" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -5058,23 +4728,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Выбирать упражнения через bottom sheet с multi-select</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
+          <t>Видеть библиотеку упражнений</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -5084,12 +4758,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Менять порядок упражнений перетаскиванием</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
+          <t>Искать упражнение по названию</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -5097,155 +4771,159 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Фильтровать по группе мышц</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Создать своё упражнение</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Видеть историю по упражнению</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Видеть личный рекорд по упражнению прямо в библиотеке</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Видеть активную тренировку</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Видеть детали упражнения</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Завершить тренировку</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Видеть длительность тренировки</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Добавить подход (вес × повторения)</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Редактировать подход</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Удалить подход</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Редактировать своё упражнение</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -5256,74 +4934,74 @@
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F24" s="16" t="n"/>
+      <c r="F24" s="16" t="inlineStr"/>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Видеть предыдущий результат по упражнению прямо во время тренировки</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Удалить своё упражнение</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F25" s="16" t="n"/>
+      <c r="F25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Таймер отдыха между подходами</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Добавить упражнение в избранное</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F26" s="16" t="n"/>
+      <c r="F26" s="16" t="inlineStr"/>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Отметить подход как выполненный</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Фильтровать по инвентарю</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Упражнения</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -5334,7 +5012,7 @@
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n"/>
+      <c r="F27" s="16" t="inlineStr"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -5344,1312 +5022,1356 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Видеть общий объём подходов (вес × повторения)</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
+          <t>Добавить подход (вес × повторения)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Подходы</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Чтобы экран не гас во время тренировки</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
+          <t>Редактировать подход</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F29" s="16" t="n"/>
+      <c r="F29" s="16" t="inlineStr"/>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Использовать custom numpad для ввода веса и повторений</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
+          <t>Удалить подход</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>Подходы</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n"/>
+      <c r="F30" s="16" t="inlineStr"/>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Чтобы новый подход заполнялся значениями прошлой тренировки</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+          <t>Видеть предыдущий результат по упражнению прямо во время тренировки</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>Подходы</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F31" s="16" t="n"/>
+      <c r="F31" s="16" t="inlineStr"/>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Чтобы pr считался по estimated 1rm формуле для справедливого сравнения</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
+          <t>Таймер отдыха между подходами</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F32" s="16" t="n"/>
+      <c r="F32" s="16" t="inlineStr"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Отметить подход как выполненный</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Настроить время таймера отдыха</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Видеть общий объём подходов (вес × повторения)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Получить уведомление когда таймер закончился</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Логировать подходы без веса (отжимания, подтягивания)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Видеть историю тренировок</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Скопировать подходы из прошлой тренировки</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>Подходы</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Видеть график прогресса по упражнению</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Видеть личный рекорд по каждому упражнению</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Получить уведомление о новом рекорде</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Логировать вес тела</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Видеть график веса тела</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Видеть статистику за период (неделя/месяц/всё время)</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr"/>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Видеть количество тренировок за период</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Видеть общий тоннаж за тренировку</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Открыть детали тренировки</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Видеть streak (серия тренировок)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Удалить тренировку</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Видеть прогресс по группам мышц</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Видеть историю по упражнению</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Видеть личный рекорд по упражнению прямо в библиотеке</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Редактировать своё упражнение</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Удалить своё упражнение</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Видеть график прогресса по упражнению</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Экспортировать статистику в pdf</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Прогресс</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Указать имя</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Сбросить пароль</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Переключать тёмную и светлую тему</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Видеть крупные кнопки и текст во время тренировки</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Минимум шагов для логирования подхода</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Быстро добавить подход одним тапом</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Крупный числовой ввод</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Продолжить незавершённую тренировку</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Чтобы удаление кастомного упражнения не ломало старые тренировки</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F49" s="16" t="n"/>
+      <c r="F49" s="16" t="inlineStr"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Отменить активную тренировку</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
+          <t>Указать имя</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="n"/>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Указать цель (сила, масса, похудение)</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Указать параметры (возраст, рост, вес)</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Видеть общую статистику профиля</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>Зарегистрироваться</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>Войти в аккаунт</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Выйти из аккаунта</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr"/>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>Сбросить пароль</t>
+        </is>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D57" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Удалить аккаунт</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="37" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B59" s="38" t="inlineStr">
+        <is>
+          <t>Войти через google</t>
+        </is>
+      </c>
+      <c r="C59" s="37" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D59" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="37" t="inlineStr">
+        <is>
+          <t>[✕] Вырезано (ADR-65)</t>
+        </is>
+      </c>
+      <c r="F59" s="41" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Изменить пароль</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr"/>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Добавить фото профиля</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Профиль</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr"/>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Переключать тёмную и светлую тему</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr"/>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Видеть детали упражнения</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Настроить время таймера отдыха</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Получить уведомление когда таймер закончился</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="n"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Видеть личный рекорд по каждому упражнению</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="n"/>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Видеть статистику за период (неделя/месяц/всё время)</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="n"/>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Видеть количество тренировок за период</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="n"/>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Видеть общий тоннаж за тренировку</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="n"/>
-    </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Указать цель (сила, масса, похудение)</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Указать параметры (возраст, рост, вес)</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="n"/>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Видеть общую статистику профиля</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="n"/>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Выйти из аккаунта</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="n">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Видеть красивую иконку приложения</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="n"/>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Удалить аккаунт</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="n"/>
-    </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Изменить пароль</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
           <t>[ ] Не начато</t>
         </is>
       </c>
-      <c r="F63" s="16" t="n"/>
+      <c r="F63" s="16" t="inlineStr"/>
     </row>
     <row r="64" ht="36" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Видеть красивую иконку приложения</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
+          <t>Выбрать единицы измерения (кг / фунты)</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr"/>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B65" s="35" t="inlineStr">
+        <is>
+          <t>Видеть splash screen при запуске</t>
+        </is>
+      </c>
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="n"/>
-    </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Выбрать единицы измерения (кг / фунты)</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F65" s="40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Получать toast уведомления об успешных действиях</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="n"/>
-    </row>
-    <row r="66" ht="36" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Видеть плавные анимации при переходах</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="D66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr"/>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Видеть empty state на пустых экранах</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="n"/>
-    </row>
-    <row r="67" ht="36" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Получать haptic feedback при нажатиях</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="D67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr"/>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>Использовать bottom navigation bar</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="inlineStr">
         <is>
           <t>Приложение</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="n"/>
-    </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Видеть гистограмму частоты тренировок</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>[ ] Не начато</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="n"/>
+      <c r="D68" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="34" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>Out of MVP</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Выбрать готовый шаблон тренировки</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
+          <t>Видеть крупные кнопки и текст во время тренировки</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Перенесено</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>Reassigned from Sprint 1 on 2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Минимум шагов для логирования подхода</t>
+        </is>
+      </c>
+      <c r="C70" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Быстро добавить подход одним тапом</t>
+        </is>
+      </c>
+      <c r="C71" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Крупный числовой ввод</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Как пользователь я хочу</t>
+        </is>
+      </c>
+      <c r="C73" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr"/>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Экспортировать данные в json</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr"/>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Получать push-уведомления с напоминанием о тренировке</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="n"/>
-    </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Сохранить тренировку как шаблон</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F70" s="16" t="n"/>
-    </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Редактировать шаблон</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="n"/>
-    </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Удалить шаблон</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="n"/>
-    </row>
-    <row r="73" ht="36" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Дублировать прошлую тренировку</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F73" s="16" t="n"/>
-    </row>
-    <row r="74" ht="36" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Добавить заметку к тренировке</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Тренировки</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="n"/>
-    </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Добавить упражнение в избранное</t>
-        </is>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr"/>
     </row>
     <row r="76" ht="36" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Фильтровать по инвентарю</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
+          <t>Импортировать данные из json</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr"/>
     </row>
     <row r="77" ht="36" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Видеть какие мышцы задействованы на схеме тела</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
+          <t>Видеть плавные анимации при переходах</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F77" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr"/>
     </row>
     <row r="78" ht="36" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Видеть сколько раз делал упражнение</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Упражнения</t>
+          <t>Получать haptic feedback при нажатиях</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -6657,25 +6379,25 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F78" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr"/>
     </row>
     <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Логировать подходы без веса (отжимания, подтягивания)</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Видеть skeleton loader пока загружаются данные</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
@@ -6683,504 +6405,306 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F79" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr"/>
     </row>
     <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Скопировать подходы из прошлой тренировки</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
+          <t>Использовать приложение одной рукой</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="inlineStr">
+        <is>
+          <t>Приложение</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Логировать кардио (время, дистанция)</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>Подходы</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F81" s="16" t="n"/>
+          <t>[ ] Не начато</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Получить уведомление о новом рекорде</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F82" s="16" t="n"/>
+      <c r="A82" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B82" s="42" t="inlineStr">
+        <is>
+          <t>Foundation: design system + theme + constants</t>
+        </is>
+      </c>
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D82" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F82" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Логировать вес тела</t>
-        </is>
-      </c>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F83" s="16" t="n"/>
+      <c r="A83" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B83" s="42" t="inlineStr">
+        <is>
+          <t>Firebase init + offline persistence + emulator hooks</t>
+        </is>
+      </c>
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Видеть график веса тела</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="n"/>
+      <c r="A84" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B84" s="42" t="inlineStr">
+        <is>
+          <t>Core widgets library (AppLogo, Buttons, Input, Divider)</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F84" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Видеть streak (серия тренировок)</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F85" s="16" t="n"/>
+      <c r="A85" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B85" s="42" t="inlineStr">
+        <is>
+          <t>go_router skeleton + Splash screen</t>
+        </is>
+      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F85" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>Видеть прогресс по группам мышц</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="n"/>
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t>AppUser model + AppException hierarchy + ErrorMapper</t>
+        </is>
+      </c>
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F86" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Экспортировать статистику в pdf</t>
-        </is>
-      </c>
-      <c r="C87" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F87" s="16" t="n"/>
+      <c r="A87" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B87" s="42" t="inlineStr">
+        <is>
+          <t>AuthService + IAuthRepository + FirebaseAuthRepository</t>
+        </is>
+      </c>
+      <c r="C87" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F87" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Сравнить две тренировки</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>Прогресс</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F88" s="16" t="n"/>
+      <c r="A88" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t>authStateProvider + AuthNotifier</t>
+        </is>
+      </c>
+      <c r="C88" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F88" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Добавить фото профиля</t>
-        </is>
-      </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F89" s="16" t="n"/>
+      <c r="A89" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>Auth redirect logic in GoRouter</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D89" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F89" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Видеть дату регистрации</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>Профиль</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n">
+      <c r="A90" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>Global dismiss-keyboard-on-tap-outside</t>
+        </is>
+      </c>
+      <c r="C90" s="42" t="inlineStr">
+        <is>
+          <t>Инфра</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F90" s="16" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Экспортировать данные в json</t>
-        </is>
-      </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F91" s="16" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Получать push-уведомления с напоминанием о тренировке</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F92" s="16" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Импортировать данные из json</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F93" s="16" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Видеть skeleton loader пока загружаются данные</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F94" s="16" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Использовать приложение одной рукой</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F95" s="16" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Выбрать язык приложения (рус/eng)</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F96" s="16" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Поделиться тренировкой</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F97" s="16" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t>Out of MVP</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Делать pull-to-refresh</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>Приложение</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>[~] Не в MVP</t>
-        </is>
-      </c>
-      <c r="F98" s="16" t="n"/>
+      <c r="E90" s="42" t="inlineStr">
+        <is>
+          <t>[x] Готово</t>
+        </is>
+      </c>
+      <c r="F90" s="42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7193,7 +6717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7244,16 +6768,16 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
@@ -7263,16 +6787,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="26" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -7282,7 +6806,7 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>3</v>
@@ -7291,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -7301,16 +6825,16 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
@@ -7342,13 +6866,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="26" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -7358,157 +6882,204 @@
         </is>
       </c>
       <c r="B10" s="33" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>8</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>MVP Scope Breakdown</t>
-        </is>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 1 — Foundation (Completed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>Stories</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>13</v>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>Вырезано</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Прогресс</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Auth flow</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>75% (Google Sign-In cut)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Foundation / infra</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>100% (design system, Firebase, router, repos, providers)</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sprint 5</t>
+          <t>User-facing screens</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100% (Splash, Login, Register, placeholders, Workout Start)</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>ИТОГО Sprint 1</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="C19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MVP Total</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>67</v>
-      </c>
-      <c r="C20" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Out of MVP (backlog)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C21" t="n">
-        <v>91</v>
+      <c r="D19" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="45" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>97</v>
-      </c>
-      <c r="C22" t="n">
-        <v>243</v>
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Key Learnings (Sprint 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>• Freezed 3.x requires `abstract class X with _$X` for factory redirects</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>• Firebase emulator needs 10.0.2.2 on Android (not localhost) + network_security_config.xml for cleartext</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>• Material TextField needs InputBorder.none on enabled/focused/disabled states to remove default underline</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>• go_router refresh must use ref.listen → ValueNotifier pattern, NOT raw Firebase stream (subscribers get out of sync)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>• Broadcast stream required in AuthRepository to share auth events between refreshListenable and StreamProvider</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>Next: Sprint 2 — Core infrastructure (models, repositories, toast, empty states)</t>
+        </is>
       </c>
     </row>
   </sheetData>
